--- a/hrd/assets/sources/attendance_sheets/28_attendance_sheet.xlsx
+++ b/hrd/assets/sources/attendance_sheets/28_attendance_sheet.xlsx
@@ -17,15 +17,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="16">
   <si>
     <t>Test Training 2026</t>
   </si>
   <si>
-    <t>June 1-2, 2025</t>
-  </si>
-  <si>
-    <t>CSC ROVI</t>
+    <t>April 27-29, 2025</t>
+  </si>
+  <si>
+    <t>Narnia Hall</t>
   </si>
   <si>
     <t>No.</t>
@@ -37,10 +37,13 @@
     <t>Agency</t>
   </si>
   <si>
-    <t>Day 1</t>
-  </si>
-  <si>
-    <t>Day 2</t>
+    <t>Day 3</t>
+  </si>
+  <si>
+    <t>Philippine Information Agency</t>
+  </si>
+  <si>
+    <t>Rayvil Cordero</t>
   </si>
   <si>
     <t>Civil Service Commission Regional Office No. VI</t>
@@ -49,13 +52,19 @@
     <t>Nicca Mae B.Senato</t>
   </si>
   <si>
+    <t>President Roxas, Capiz</t>
+  </si>
+  <si>
+    <t>Gov.  Emily Sinclair</t>
+  </si>
+  <si>
     <t>Chad Gian G.Villanueva</t>
   </si>
   <si>
-    <t>Rayvil Cordero</t>
-  </si>
-  <si>
-    <t>Philippine Information Agency</t>
+    <t>Atty.  Arnel B.Fernandez</t>
+  </si>
+  <si>
+    <t>CSC</t>
   </si>
 </sst>
 </file>
@@ -137,7 +146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -171,6 +180,9 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
   </cellXfs>
@@ -548,95 +560,84 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="true" style="3"/>
-    <col min="2" max="2" width="54.85546875" customWidth="true" style="4"/>
-    <col min="3" max="3" width="54.85546875" customWidth="true" style="4"/>
+    <col min="2" max="2" width="62.7109375" customWidth="true" style="4"/>
+    <col min="3" max="3" width="66.42578125" customWidth="true" style="4"/>
     <col min="4" max="4" width="18.28515625" customWidth="true" style="4"/>
-    <col min="5" max="5" width="18.28515625" customWidth="true" style="4"/>
-    <col min="6" max="6" width="9.140625" customWidth="true" style="4"/>
+    <col min="5" max="5" width="9.140625" customWidth="true" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1">
+    <row r="1" spans="1:5" s="1" customFormat="1">
       <c r="A1" s="10"/>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-    </row>
-    <row r="2" spans="1:6" s="1" customFormat="1">
+    </row>
+    <row r="2" spans="1:5" s="1" customFormat="1">
       <c r="A2" s="9"/>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-    </row>
-    <row r="3" spans="1:6" s="1" customFormat="1">
+    </row>
+    <row r="3" spans="1:5" s="1" customFormat="1">
       <c r="A3" s="9"/>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
       <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-    </row>
-    <row r="4" spans="1:6" s="1" customFormat="1">
+    </row>
+    <row r="4" spans="1:5" s="1" customFormat="1">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-    </row>
-    <row r="5" spans="1:6" s="1" customFormat="1">
+    </row>
+    <row r="5" spans="1:5" s="1" customFormat="1">
       <c r="A5" s="9"/>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-    </row>
-    <row r="6" spans="1:6" s="1" customFormat="1">
+    </row>
+    <row r="6" spans="1:5" s="1" customFormat="1">
       <c r="A6" s="9"/>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-    </row>
-    <row r="7" spans="1:6" s="1" customFormat="1">
+    </row>
+    <row r="7" spans="1:5" s="1" customFormat="1">
       <c r="A7" s="9"/>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-    </row>
-    <row r="8" spans="1:6" customHeight="1" ht="15.75" s="1" customFormat="1">
+    </row>
+    <row r="8" spans="1:5" customHeight="1" ht="15.75" s="1" customFormat="1">
       <c r="A8" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-    </row>
-    <row r="9" spans="1:6" customHeight="1" ht="19.5" s="1" customFormat="1">
+    </row>
+    <row r="9" spans="1:5" customHeight="1" ht="19.5" s="1" customFormat="1">
       <c r="A9" s="8" t="s">
         <v>1</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-    </row>
-    <row r="10" spans="1:6" s="1" customFormat="1">
+    </row>
+    <row r="10" spans="1:5" s="1" customFormat="1">
       <c r="A10" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-    </row>
-    <row r="11" spans="1:6" s="1" customFormat="1"/>
-    <row r="12" spans="1:6" customHeight="1" ht="24" s="3" customFormat="1">
+    </row>
+    <row r="11" spans="1:5" s="1" customFormat="1"/>
+    <row r="12" spans="1:5" customHeight="1" ht="24" s="3" customFormat="1">
       <c r="A12" s="2" t="s">
         <v>3</v>
       </c>
@@ -649,167 +650,175 @@
       <c r="D12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" customHeight="1" ht="24">
+    </row>
+    <row r="13" spans="1:5" customHeight="1" ht="24">
       <c r="A13" s="11">
         <v>1</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-    </row>
-    <row r="14" spans="1:6" customHeight="1" ht="24">
+      <c r="E13" s="13"/>
+    </row>
+    <row r="14" spans="1:5" customHeight="1" ht="24">
       <c r="A14" s="11">
         <v>2</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-    </row>
-    <row r="15" spans="1:6" customHeight="1" ht="24">
+      <c r="E14" s="13"/>
+    </row>
+    <row r="15" spans="1:5" customHeight="1" ht="24">
       <c r="A15" s="11">
         <v>3</v>
       </c>
       <c r="B15" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="11"/>
+      <c r="E15" s="13"/>
+    </row>
+    <row r="16" spans="1:5" customHeight="1" ht="24">
+      <c r="A16" s="11">
+        <v>4</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="D16" s="11"/>
+      <c r="E16" s="13"/>
+    </row>
+    <row r="17" spans="1:5" customHeight="1" ht="24">
+      <c r="A17" s="11">
+        <v>5</v>
+      </c>
+      <c r="B17" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-    </row>
-    <row r="16" spans="1:6" customHeight="1" ht="22.5">
-      <c r="A16" s="11"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-    </row>
-    <row r="17" spans="1:6" customHeight="1" ht="22.5">
-      <c r="A17" s="5"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-    </row>
-    <row r="18" spans="1:6" customHeight="1" ht="22.5">
-      <c r="A18" s="5"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-    </row>
-    <row r="19" spans="1:6" customHeight="1" ht="22.5">
+      <c r="C17" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="11"/>
+      <c r="E17" s="13"/>
+    </row>
+    <row r="18" spans="1:5" customHeight="1" ht="22.5">
+      <c r="A18" s="11"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="13"/>
+    </row>
+    <row r="19" spans="1:5" customHeight="1" ht="22.5">
       <c r="A19" s="5"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-    </row>
-    <row r="20" spans="1:6" customHeight="1" ht="22.5">
+    </row>
+    <row r="20" spans="1:5" customHeight="1" ht="22.5">
       <c r="A20" s="5"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-    </row>
-    <row r="21" spans="1:6" customHeight="1" ht="22.5">
+    </row>
+    <row r="21" spans="1:5" customHeight="1" ht="22.5">
       <c r="A21" s="5"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-    </row>
-    <row r="22" spans="1:6" customHeight="1" ht="22.5">
+    </row>
+    <row r="22" spans="1:5" customHeight="1" ht="22.5">
       <c r="A22" s="5"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-    </row>
-    <row r="23" spans="1:6" customHeight="1" ht="22.5">
+    </row>
+    <row r="23" spans="1:5" customHeight="1" ht="22.5">
       <c r="A23" s="5"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-    </row>
-    <row r="24" spans="1:6" customHeight="1" ht="22.5">
+    </row>
+    <row r="24" spans="1:5" customHeight="1" ht="22.5">
       <c r="A24" s="5"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-    </row>
-    <row r="25" spans="1:6" customHeight="1" ht="22.5">
+    </row>
+    <row r="25" spans="1:5" customHeight="1" ht="22.5">
       <c r="A25" s="5"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-    </row>
-    <row r="26" spans="1:6" customHeight="1" ht="22.5">
+    </row>
+    <row r="26" spans="1:5" customHeight="1" ht="22.5">
       <c r="A26" s="5"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-    </row>
-    <row r="27" spans="1:6" customHeight="1" ht="22.5">
+    </row>
+    <row r="27" spans="1:5" customHeight="1" ht="22.5">
       <c r="A27" s="5"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-    </row>
-    <row r="28" spans="1:6" customHeight="1" ht="22.5">
+    </row>
+    <row r="28" spans="1:5" customHeight="1" ht="22.5">
       <c r="A28" s="5"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-    </row>
-    <row r="29" spans="1:6" customHeight="1" ht="22.5">
+    </row>
+    <row r="29" spans="1:5" customHeight="1" ht="22.5">
       <c r="A29" s="5"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-    </row>
-    <row r="30" spans="1:6" customHeight="1" ht="22.5">
+    </row>
+    <row r="30" spans="1:5" customHeight="1" ht="22.5">
       <c r="A30" s="5"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-    </row>
-    <row r="31" spans="1:6" customHeight="1" ht="22.5">
+    </row>
+    <row r="31" spans="1:5" customHeight="1" ht="22.5">
       <c r="A31" s="5"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
+    </row>
+    <row r="32" spans="1:5" customHeight="1" ht="22.5">
+      <c r="A32" s="5"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+    </row>
+    <row r="33" spans="1:5" customHeight="1" ht="22.5">
+      <c r="A33" s="5"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
     </row>
   </sheetData>
   <mergeCells>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A1:E7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A1:D7"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true" horizontalCentered="true"/>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.5" header="0" footer="0"/>
